--- a/datasets/QHI_roots_data/QHI_combined_data.xlsx
+++ b/datasets/QHI_roots_data/QHI_combined_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2277781_ed_ac_uk/Documents/Dissertation/Data/QHI_root_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{2CE744FD-1DF3-4494-920D-C80FD1825ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0EC3F3D-9441-48C3-81AF-A9B418F70A3C}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{2CE744FD-1DF3-4494-920D-C80FD1825ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C421BC9E-48B1-41E3-8B72-41ED1E504B47}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6E0FEA08-AC88-4468-891C-41C0FB8544C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="50">
   <si>
     <t>subplot</t>
   </si>
@@ -174,6 +174,18 @@
   </si>
   <si>
     <t>max_depth_increment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QHI12 </t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P6</t>
   </si>
 </sst>
 </file>
@@ -536,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -729,9 +741,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,10 +757,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75C4B54-88DB-4B80-9D1B-55B531190FB3}">
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="5" width="16.33203125" customWidth="1"/>
@@ -1165,7 +1170,7 @@
       <c r="D3" s="4">
         <v>42125</v>
       </c>
-      <c r="E3" s="65">
+      <c r="E3" s="55">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1235,7 +1240,7 @@
       <c r="D5" s="4">
         <v>42125</v>
       </c>
-      <c r="E5" s="65">
+      <c r="E5" s="55">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1340,7 +1345,7 @@
       <c r="D8" s="4">
         <v>42125</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="55">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1480,7 +1485,7 @@
       <c r="D12" s="3">
         <v>45935</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="55">
         <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1550,7 +1555,7 @@
       <c r="D14" s="4">
         <v>42125</v>
       </c>
-      <c r="E14" s="65">
+      <c r="E14" s="55">
         <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1655,7 +1660,7 @@
       <c r="D17" s="4">
         <v>42125</v>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="55">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1795,7 +1800,7 @@
       <c r="D21" s="3">
         <v>45935</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="55">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1865,7 +1870,7 @@
       <c r="D23" s="4">
         <v>42125</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E23" s="55">
         <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -1970,7 +1975,7 @@
       <c r="D26" s="4">
         <v>42125</v>
       </c>
-      <c r="E26" s="65">
+      <c r="E26" s="55">
         <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2110,7 +2115,7 @@
       <c r="D30" s="3">
         <v>45935</v>
       </c>
-      <c r="E30" s="65">
+      <c r="E30" s="55">
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -2180,7 +2185,7 @@
       <c r="D32" s="4">
         <v>42125</v>
       </c>
-      <c r="E32" s="65">
+      <c r="E32" s="55">
         <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2320,7 +2325,7 @@
       <c r="D36" s="4">
         <v>42125</v>
       </c>
-      <c r="E36" s="65">
+      <c r="E36" s="55">
         <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2460,7 +2465,7 @@
       <c r="D40" s="3">
         <v>45935</v>
       </c>
-      <c r="E40" s="65">
+      <c r="E40" s="55">
         <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -2565,7 +2570,7 @@
       <c r="D43" s="4">
         <v>42125</v>
       </c>
-      <c r="E43" s="65">
+      <c r="E43" s="55">
         <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -2705,7 +2710,7 @@
       <c r="D47" s="3">
         <v>45935</v>
       </c>
-      <c r="E47" s="65">
+      <c r="E47" s="55">
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -2775,7 +2780,7 @@
       <c r="D49" s="4">
         <v>42125</v>
       </c>
-      <c r="E49" s="65">
+      <c r="E49" s="55">
         <v>15</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -2880,7 +2885,7 @@
       <c r="D52" s="4">
         <v>42125</v>
       </c>
-      <c r="E52" s="65">
+      <c r="E52" s="55">
         <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -3020,7 +3025,7 @@
       <c r="D56" s="3">
         <v>45935</v>
       </c>
-      <c r="E56" s="65">
+      <c r="E56" s="55">
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -3090,7 +3095,7 @@
       <c r="D58" s="4">
         <v>42125</v>
       </c>
-      <c r="E58" s="65">
+      <c r="E58" s="55">
         <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -3195,7 +3200,7 @@
       <c r="D61" s="4">
         <v>42125</v>
       </c>
-      <c r="E61" s="65">
+      <c r="E61" s="55">
         <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -3335,7 +3340,7 @@
       <c r="D65" s="3">
         <v>45935</v>
       </c>
-      <c r="E65" s="65">
+      <c r="E65" s="55">
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -3405,7 +3410,7 @@
       <c r="D67" s="4">
         <v>42125</v>
       </c>
-      <c r="E67" s="65">
+      <c r="E67" s="55">
         <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -3510,7 +3515,7 @@
       <c r="D70" s="4">
         <v>42125</v>
       </c>
-      <c r="E70" s="65">
+      <c r="E70" s="55">
         <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -3650,7 +3655,7 @@
       <c r="D74" s="3">
         <v>45935</v>
       </c>
-      <c r="E74" s="65">
+      <c r="E74" s="55">
         <v>10</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -3720,7 +3725,7 @@
       <c r="D76" s="4">
         <v>42125</v>
       </c>
-      <c r="E76" s="65">
+      <c r="E76" s="55">
         <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -3825,7 +3830,7 @@
       <c r="D79" s="4">
         <v>42125</v>
       </c>
-      <c r="E79" s="65">
+      <c r="E79" s="55">
         <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -3965,7 +3970,7 @@
       <c r="D83" s="3">
         <v>45935</v>
       </c>
-      <c r="E83" s="65">
+      <c r="E83" s="55">
         <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -4035,7 +4040,7 @@
       <c r="D85" s="4">
         <v>42125</v>
       </c>
-      <c r="E85" s="65">
+      <c r="E85" s="55">
         <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -4140,7 +4145,7 @@
       <c r="D88" s="4">
         <v>42125</v>
       </c>
-      <c r="E88" s="65">
+      <c r="E88" s="55">
         <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -4280,7 +4285,7 @@
       <c r="D92" s="3">
         <v>45935</v>
       </c>
-      <c r="E92" s="65">
+      <c r="E92" s="55">
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -4350,7 +4355,7 @@
       <c r="D94" s="4">
         <v>42125</v>
       </c>
-      <c r="E94" s="65">
+      <c r="E94" s="55">
         <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -4455,7 +4460,7 @@
       <c r="D97" s="4">
         <v>42125</v>
       </c>
-      <c r="E97" s="65">
+      <c r="E97" s="55">
         <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
@@ -4595,7 +4600,7 @@
       <c r="D101" s="3">
         <v>45935</v>
       </c>
-      <c r="E101" s="65">
+      <c r="E101" s="55">
         <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -4665,7 +4670,7 @@
       <c r="D103" s="4">
         <v>42125</v>
       </c>
-      <c r="E103" s="65">
+      <c r="E103" s="55">
         <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
@@ -4770,7 +4775,7 @@
       <c r="D106" s="4">
         <v>42125</v>
       </c>
-      <c r="E106" s="65">
+      <c r="E106" s="55">
         <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -4907,7 +4912,7 @@
       <c r="D110" s="3">
         <v>45935</v>
       </c>
-      <c r="E110" s="65">
+      <c r="E110" s="55">
         <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
@@ -4971,7 +4976,7 @@
       <c r="D112" s="4">
         <v>42125</v>
       </c>
-      <c r="E112" s="65">
+      <c r="E112" s="55">
         <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
@@ -5067,7 +5072,7 @@
       <c r="D115" s="4">
         <v>42125</v>
       </c>
-      <c r="E115" s="65">
+      <c r="E115" s="55">
         <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -5198,7 +5203,7 @@
       <c r="D119" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="E119" s="65">
+      <c r="E119" s="55">
         <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
@@ -5268,7 +5273,7 @@
       <c r="D121" s="4">
         <v>42125</v>
       </c>
-      <c r="E121" s="65">
+      <c r="E121" s="55">
         <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
@@ -5373,7 +5378,7 @@
       <c r="D124" s="56">
         <v>42125</v>
       </c>
-      <c r="E124" s="65">
+      <c r="E124" s="55">
         <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
@@ -5513,7 +5518,7 @@
       <c r="D128" s="3">
         <v>45935</v>
       </c>
-      <c r="E128" s="65">
+      <c r="E128" s="55">
         <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
@@ -5583,7 +5588,7 @@
       <c r="D130" s="4">
         <v>42125</v>
       </c>
-      <c r="E130" s="65">
+      <c r="E130" s="55">
         <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
@@ -5688,7 +5693,7 @@
       <c r="D133" s="4">
         <v>42125</v>
       </c>
-      <c r="E133" s="65">
+      <c r="E133" s="55">
         <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
@@ -5778,6 +5783,146 @@
       </c>
       <c r="K135" s="16">
         <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>2024</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E136" s="2">
+        <v>5</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H136" s="9">
+        <v>-3.1328707259999998E-2</v>
+      </c>
+      <c r="I136" s="9">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J136" s="9">
+        <v>1.1591455859999999E-3</v>
+      </c>
+      <c r="K136" s="16">
+        <v>-1.9151763749999998E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A137">
+        <v>2024</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D137" s="4">
+        <v>42125</v>
+      </c>
+      <c r="E137" s="55">
+        <v>15</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H137" s="9">
+        <v>0.1009887037</v>
+      </c>
+      <c r="I137" s="9">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="J137" s="9">
+        <v>1.030410361E-4</v>
+      </c>
+      <c r="K137" s="15">
+        <v>4.3569229420000001E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A138">
+        <v>2024</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E138" s="5">
+        <v>25</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H138" s="9">
+        <v>9.3643610710000005E-2</v>
+      </c>
+      <c r="I138" s="9">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="J138" s="9">
+        <v>2.307021899E-4</v>
+      </c>
+      <c r="K138" s="23">
+        <v>9.7176944919999994E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A139">
+        <v>2024</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E139" s="6">
+        <v>30</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H139" s="9">
+        <v>6.8509225389999998E-2</v>
+      </c>
+      <c r="I139" s="9">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J139" s="9">
+        <v>6.8315283840000005E-4</v>
+      </c>
+      <c r="K139" s="13">
+        <v>0.15910266009999999</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/QHI_roots_data/QHI_combined_data.xlsx
+++ b/datasets/QHI_roots_data/QHI_combined_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoe-my.sharepoint.com/personal/s2277781_ed_ac_uk/Documents/Dissertation/Data/QHI_root_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{2CE744FD-1DF3-4494-920D-C80FD1825ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C421BC9E-48B1-41E3-8B72-41ED1E504B47}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{2CE744FD-1DF3-4494-920D-C80FD1825ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDB84ED8-F3A0-410E-9933-D05259A0C84A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6E0FEA08-AC88-4468-891C-41C0FB8544C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="47">
   <si>
     <t>subplot</t>
   </si>
@@ -177,15 +177,6 @@
   </si>
   <si>
     <t xml:space="preserve">QHI12 </t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
-    <t>P6</t>
   </si>
 </sst>
 </file>
@@ -5828,7 +5819,7 @@
         <v>46</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D137" s="4">
         <v>42125</v>
@@ -5863,7 +5854,7 @@
         <v>46</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>26</v>
@@ -5898,7 +5889,7 @@
         <v>46</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>27</v>
